--- a/public/administrative-personnel-dashboard/hiring/FT-RH-04.xlsx
+++ b/public/administrative-personnel-dashboard/hiring/FT-RH-04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tics\Desktop\sicap\sicapsystem\public\hiring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LGress\Desktop\sicapsystem\public\administrative-personnel-dashboard\hiring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B749F5-F7BB-4455-9CB4-1FF727A7D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074DB2DB-53C3-4BF1-9F23-FBB1B44452D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1650" windowWidth="26475" windowHeight="10440" xr2:uid="{80D49D2A-8D89-4CA9-B922-F8A59A9140E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{80D49D2A-8D89-4CA9-B922-F8A59A9140E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Sigersa Innovaciones  S.A. de C.V.</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>Fotografia</t>
-  </si>
-  <si>
-    <t>Folletos de inducción</t>
   </si>
   <si>
     <t>Nombre y firma del contratado:</t>
@@ -304,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,6 +342,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -354,20 +366,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,67 +801,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="18"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="18" t="s">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="21"/>
+      <c r="I2" s="17"/>
       <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18" t="s">
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
@@ -879,13 +879,13 @@
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -896,13 +896,13 @@
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -913,13 +913,13 @@
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -930,13 +930,13 @@
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -947,13 +947,13 @@
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -964,13 +964,13 @@
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -981,13 +981,13 @@
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -1069,154 +1069,152 @@
     </row>
     <row r="18" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="12"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
       <c r="L18" s="12"/>
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="12"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
       <c r="L19" s="12"/>
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="12"/>
       <c r="G20" s="11"/>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
       <c r="L20" s="12"/>
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="12"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
       <c r="L21" s="12"/>
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="12"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
       <c r="L22" s="12"/>
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="12"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
       <c r="L23" s="12"/>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="12"/>
       <c r="G24" s="11"/>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
       <c r="L24" s="12"/>
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="12"/>
       <c r="G25" s="11"/>
-      <c r="H25" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="12"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="22"/>
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
@@ -1507,65 +1505,65 @@
     <row r="45" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
       <c r="B45" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
       <c r="M45" s="7"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
-      <c r="B46" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
+      <c r="B46" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="6"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
       <c r="M47" s="7"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
       <c r="M48" s="7"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -1590,10 +1588,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="6"/>
-      <c r="K54" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="L54" s="16"/>
+      <c r="K54" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" s="21"/>
       <c r="M54" s="7"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
@@ -1613,15 +1611,24 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F45:L45"/>
+    <mergeCell ref="B46:L48"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="H18:K18"/>
     <mergeCell ref="F12:L12"/>
@@ -1638,27 +1645,18 @@
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:L45"/>
-    <mergeCell ref="B46:L48"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0.11811023622047245" footer="0.11811023622047245"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>